--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3208AA-84A5-49EA-A566-918ADFEF618C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E37A53-AA92-4555-8824-C0C7137E1251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6024" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6076" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3574,6 +3574,29 @@
         <v>85</v>
       </c>
     </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>2026</v>
+      </c>
+      <c r="B124" t="s">
+        <v>42</v>
+      </c>
+      <c r="C124">
+        <v>820</v>
+      </c>
+      <c r="D124">
+        <v>550</v>
+      </c>
+      <c r="E124">
+        <v>73</v>
+      </c>
+      <c r="F124">
+        <v>157</v>
+      </c>
+      <c r="G124" s="17">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3582,7 +3605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6335,6 +6358,29 @@
       </c>
       <c r="G123">
         <v>4.93</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>2026</v>
+      </c>
+      <c r="B124" t="s">
+        <v>42</v>
+      </c>
+      <c r="C124">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D124">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="E124">
+        <v>4.7</v>
+      </c>
+      <c r="F124">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="G124">
+        <v>4.8899999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -6345,7 +6391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2881"/>
+  <dimension ref="A1:L2906"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -64016,6 +64062,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2882" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2882" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2882" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2882" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2882" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2882" s="3">
+        <v>753</v>
+      </c>
+      <c r="F2882" s="9">
+        <v>0.91800000000000004</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2883" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2883" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2883" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2883" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2883" s="3">
+        <v>57</v>
+      </c>
+      <c r="F2883" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2884" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2884" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2884" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2884" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2884" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2884" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2885" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2885" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2885" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2885" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2885" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2885" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2886" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2886" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2886" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2886" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2886" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2886" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2887" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2887" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2887" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2887" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2887" s="3">
+        <v>493</v>
+      </c>
+      <c r="F2887" s="9">
+        <v>0.89600000000000002</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2888" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2888" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2888" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2888" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2888" s="3">
+        <v>39</v>
+      </c>
+      <c r="F2888" s="9">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2889" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2889" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2889" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2889" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2889" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2889" s="9">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2890" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2890" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2890" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2890" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2890" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2890" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2891" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2891" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2891" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2891" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2891" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2891" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2892" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2892" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2892" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2892" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2892" s="3">
+        <v>56</v>
+      </c>
+      <c r="F2892" s="9">
+        <v>0.76700000000000002</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2893" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2893" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2893" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2893" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2893" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2893" s="9">
+        <v>0.17799999999999999</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2894" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2894" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2894" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2894" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2894" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2894" s="9">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2895" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2895" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2895" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2895" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2895" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2895" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2896" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2896" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2896" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2896" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2896" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2896" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2897" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2897" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2897" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2897" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2897" s="3">
+        <v>140</v>
+      </c>
+      <c r="F2897" s="9">
+        <v>0.89200000000000002</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2898" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2898" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2898" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2898" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2898" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2898" s="9">
+        <v>8.8999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2899" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2899" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2899" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2899" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2899" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2899" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2900" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2900" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2900" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2900" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2900" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2900" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2901" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2901" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2901" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2901" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2901" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2901" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2902" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2902" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2902" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2902" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2902" s="3">
+        <v>59</v>
+      </c>
+      <c r="F2902" s="9">
+        <v>0.89400000000000002</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2903" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2903" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2903" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2903" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2903" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2903" s="9">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2904" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2904" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2904" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2904" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2904" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2904" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2905" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2905" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2905" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2905" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2905" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2905" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2906" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2906" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2906" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2906" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2906" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2906" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E37A53-AA92-4555-8824-C0C7137E1251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF4AD7B-5CD1-4D8D-A2B7-191BEE88232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6076" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6128" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3597,6 +3597,29 @@
         <v>66</v>
       </c>
     </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>2026</v>
+      </c>
+      <c r="B125" t="s">
+        <v>43</v>
+      </c>
+      <c r="C125">
+        <v>731</v>
+      </c>
+      <c r="D125">
+        <v>470</v>
+      </c>
+      <c r="E125">
+        <v>107</v>
+      </c>
+      <c r="F125">
+        <v>148</v>
+      </c>
+      <c r="G125" s="17">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3605,7 +3628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6381,6 +6404,29 @@
       </c>
       <c r="G124">
         <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>2026</v>
+      </c>
+      <c r="B125" t="s">
+        <v>43</v>
+      </c>
+      <c r="C125">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D125">
+        <v>4.87</v>
+      </c>
+      <c r="E125">
+        <v>4.71</v>
+      </c>
+      <c r="F125">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G125">
+        <v>4.88</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6437,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2906"/>
+  <dimension ref="A1:L2931"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -64562,6 +64608,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2907" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2907" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2907" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2907" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2907" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2907" s="3">
+        <v>669</v>
+      </c>
+      <c r="F2907" s="9">
+        <v>0.91500000000000004</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2908" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2908" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2908" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2908" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2908" s="3">
+        <v>48</v>
+      </c>
+      <c r="F2908" s="9">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2909" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2909" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2909" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2909" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2909" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2909" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2910" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2910" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2910" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2910" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2910" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2910" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2911" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2911" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2911" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2911" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2911" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2911" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2912" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2912" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2912" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2912" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2912" s="3">
+        <v>431</v>
+      </c>
+      <c r="F2912" s="9">
+        <v>0.91700000000000004</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2913" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2913" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2913" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2913" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2913" s="3">
+        <v>22</v>
+      </c>
+      <c r="F2913" s="9">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2914" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2914" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2914" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2914" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2914" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2914" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2915" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2915" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2915" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2915" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2915" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2915" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2916" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2916" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2916" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2916" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2916" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2916" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2917" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2917" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2917" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2917" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2917" s="3">
+        <v>83</v>
+      </c>
+      <c r="F2917" s="9">
+        <v>0.77600000000000002</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2918" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2918" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2918" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2918" s="3">
+        <v>17</v>
+      </c>
+      <c r="F2918" s="9">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2919" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2919" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2919" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2919" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2919" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2919" s="9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2920" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2920" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2920" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2920" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2920" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2920" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2921" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2921" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2921" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2921" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2921" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2921" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2921" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2922" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2922" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2922" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2922" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2922" s="3">
+        <v>133</v>
+      </c>
+      <c r="F2922" s="9">
+        <v>0.89900000000000002</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2923" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2923" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2923" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2923" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2923" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2923" s="9">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2924" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2924" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2924" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2924" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2924" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2924" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2925" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2925" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2925" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2925" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2925" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2925" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2926" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2926" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2926" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2926" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2926" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2926" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2927" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2927" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2927" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2927" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2927" s="3">
+        <v>66</v>
+      </c>
+      <c r="F2927" s="9">
+        <v>0.89200000000000002</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2928" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2928" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2928" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2928" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2928" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2928" s="9">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2929" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2929" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2929" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2929" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2929" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2929" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2929" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2930" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2930" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2930" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2930" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2930" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2930" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2930" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2931" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2931" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2931" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2931" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2931" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2931" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2931" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF4AD7B-5CD1-4D8D-A2B7-191BEE88232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05856F71-62BD-477E-BCD6-F007DC724775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6128" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6180" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3620,6 +3620,29 @@
         <v>74</v>
       </c>
     </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>2026</v>
+      </c>
+      <c r="B126" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126">
+        <v>755</v>
+      </c>
+      <c r="D126">
+        <v>534</v>
+      </c>
+      <c r="E126">
+        <v>82</v>
+      </c>
+      <c r="F126">
+        <v>172</v>
+      </c>
+      <c r="G126" s="17">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3628,7 +3651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6427,6 +6450,29 @@
       </c>
       <c r="G125">
         <v>4.88</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>2026</v>
+      </c>
+      <c r="B126" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D126">
+        <v>4.92</v>
+      </c>
+      <c r="E126">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F126">
+        <v>4.92</v>
+      </c>
+      <c r="G126">
+        <v>4.8899999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -6437,7 +6483,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2931"/>
+  <dimension ref="A1:L2956"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -65108,6 +65154,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2932" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2932" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2932" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2932" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2932" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2932" s="3">
+        <v>687</v>
+      </c>
+      <c r="F2932" s="9">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="2933" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2933" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2933" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2933" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2933" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2933" s="3">
+        <v>57</v>
+      </c>
+      <c r="F2933" s="9">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2934" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2934" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2934" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2934" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2934" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2934" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2934" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2935" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2935" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2935" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2935" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2935" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2935" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2935" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2936" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2936" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2936" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2936" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2936" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2936" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2936" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2937" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2937" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2937" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2937" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2937" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2937" s="3">
+        <v>499</v>
+      </c>
+      <c r="F2937" s="9">
+        <v>0.93400000000000005</v>
+      </c>
+    </row>
+    <row r="2938" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2938" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2938" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2938" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2938" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2938" s="3">
+        <v>28</v>
+      </c>
+      <c r="F2938" s="9">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2939" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2939" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2939" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2939" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2939" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2939" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2939" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="2940" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2940" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2940" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2940" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2940" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2940" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2940" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2941" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2941" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2941" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2941" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2941" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2941" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2941" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2942" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2942" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2942" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2942" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2942" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2942" s="3">
+        <v>74</v>
+      </c>
+      <c r="F2942" s="9">
+        <v>0.90200000000000002</v>
+      </c>
+    </row>
+    <row r="2943" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2943" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2943" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2943" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2943" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2943" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2943" s="9">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="2944" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2944" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2944" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2944" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2944" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2944" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2944" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2945" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2945" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2945" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2945" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2945" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2945" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2945" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2946" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2946" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2946" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2946" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2946" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2946" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2946" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2947" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2947" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2947" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2947" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2947" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2947" s="3">
+        <v>163</v>
+      </c>
+      <c r="F2947" s="9">
+        <v>0.94799999999999995</v>
+      </c>
+    </row>
+    <row r="2948" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2948" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2948" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2948" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2948" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2948" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2948" s="9">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2949" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2949" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2949" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2949" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2949" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2949" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2949" s="9">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="2950" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2950" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2950" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2950" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2950" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2950" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2950" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2951" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2951" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2951" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2951" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2951" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2951" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2951" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2952" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2952" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2952" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2952" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2952" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2952" s="3">
+        <v>71</v>
+      </c>
+      <c r="F2952" s="9">
+        <v>0.94699999999999995</v>
+      </c>
+    </row>
+    <row r="2953" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2953" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2953" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2953" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2953" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2953" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2953" s="9">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="2954" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2954" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2954" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2954" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2954" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2954" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2954" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2955" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2955" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2955" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2955" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2955" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2955" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2955" s="9">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="2956" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2956" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2956" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2956" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2956" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2956" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2956" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05856F71-62BD-477E-BCD6-F007DC724775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C9F1CE-8683-4A2A-8FA4-AE4DC42C020A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6180" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6232" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3643,6 +3643,29 @@
         <v>75</v>
       </c>
     </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>2026</v>
+      </c>
+      <c r="B127" t="s">
+        <v>45</v>
+      </c>
+      <c r="C127">
+        <v>698</v>
+      </c>
+      <c r="D127">
+        <v>565</v>
+      </c>
+      <c r="E127">
+        <v>85</v>
+      </c>
+      <c r="F127">
+        <v>169</v>
+      </c>
+      <c r="G127" s="17">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3651,7 +3674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6473,6 +6496,29 @@
       </c>
       <c r="G126">
         <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>2026</v>
+      </c>
+      <c r="B127" t="s">
+        <v>45</v>
+      </c>
+      <c r="C127">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D127">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E127">
+        <v>4.75</v>
+      </c>
+      <c r="F127">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="G127">
+        <v>4.87</v>
       </c>
     </row>
   </sheetData>
@@ -6483,7 +6529,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2956"/>
+  <dimension ref="A1:L2981"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -65654,6 +65700,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2957" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2957" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2957" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2957" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2957" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2957" s="3">
+        <v>637</v>
+      </c>
+      <c r="F2957" s="9">
+        <v>0.91300000000000003</v>
+      </c>
+    </row>
+    <row r="2958" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2958" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2958" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2958" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2958" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2958" s="3">
+        <v>49</v>
+      </c>
+      <c r="F2958" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2959" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2959" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2959" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2959" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2959" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2959" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2959" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2960" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2960" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2960" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2960" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2960" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2960" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2960" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2961" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2961" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2961" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2961" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2961" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2961" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2962" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2962" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2962" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2962" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2962" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2962" s="3">
+        <v>526</v>
+      </c>
+      <c r="F2962" s="9">
+        <v>0.93100000000000005</v>
+      </c>
+    </row>
+    <row r="2963" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2963" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2963" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2963" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2963" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2963" s="3">
+        <v>29</v>
+      </c>
+      <c r="F2963" s="9">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2964" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2964" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2964" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2964" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2964" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2964" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2964" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2965" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2965" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2965" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2965" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2965" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2965" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2965" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2966" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2966" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2966" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2966" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2966" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2966" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2966" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2967" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2967" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2967" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2967" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2967" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2967" s="3">
+        <v>71</v>
+      </c>
+      <c r="F2967" s="9">
+        <v>0.83499999999999996</v>
+      </c>
+    </row>
+    <row r="2968" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2968" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2968" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2968" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2968" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2968" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2968" s="9">
+        <v>0.11799999999999999</v>
+      </c>
+    </row>
+    <row r="2969" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2969" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2969" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2969" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2969" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2969" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2969" s="9">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="2970" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2970" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2970" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2970" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2970" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2970" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2970" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2971" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2971" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2971" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2971" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2971" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2971" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2971" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2972" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2972" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2972" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2972" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2972" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2972" s="3">
+        <v>153</v>
+      </c>
+      <c r="F2972" s="9">
+        <v>0.90500000000000003</v>
+      </c>
+    </row>
+    <row r="2973" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2973" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2973" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2973" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2973" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2973" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2973" s="9">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="2974" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2974" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2974" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2974" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2974" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2974" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2974" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2975" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2975" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2975" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2975" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2975" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2975" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2975" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2976" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2976" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2976" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2976" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2976" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2976" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2976" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2977" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2977" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2977" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2977" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2977" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2977" s="3">
+        <v>68</v>
+      </c>
+      <c r="F2977" s="9">
+        <v>0.89500000000000002</v>
+      </c>
+    </row>
+    <row r="2978" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2978" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2978" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2978" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2978" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2978" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2978" s="9">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2979" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2979" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2979" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2979" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2979" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2979" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2979" s="9">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2980" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2980" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2980" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2980" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2980" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2980" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2980" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2981" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2981" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2981" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2981" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2981" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2981" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2981" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C9F1CE-8683-4A2A-8FA4-AE4DC42C020A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A4B614-C1AD-4CD0-A5D3-EADC99313905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6232" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6284" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3666,6 +3666,29 @@
         <v>76</v>
       </c>
     </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>2026</v>
+      </c>
+      <c r="B128" t="s">
+        <v>46</v>
+      </c>
+      <c r="C128">
+        <v>770</v>
+      </c>
+      <c r="D128">
+        <v>561</v>
+      </c>
+      <c r="E128">
+        <v>81</v>
+      </c>
+      <c r="F128">
+        <v>169</v>
+      </c>
+      <c r="G128" s="17">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3674,7 +3697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6519,6 +6542,29 @@
       </c>
       <c r="G127">
         <v>4.87</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>2026</v>
+      </c>
+      <c r="B128" t="s">
+        <v>46</v>
+      </c>
+      <c r="C128">
+        <v>4.93</v>
+      </c>
+      <c r="D128">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="E128">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="F128">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G128">
+        <v>4.93</v>
       </c>
     </row>
   </sheetData>
@@ -6529,7 +6575,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2981"/>
+  <dimension ref="A1:L3006"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -66200,6 +66246,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2982" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2982" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2982" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2982" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2982" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2982" s="3">
+        <v>727</v>
+      </c>
+      <c r="F2982" s="9">
+        <v>0.94399999999999995</v>
+      </c>
+    </row>
+    <row r="2983" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2983" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2983" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2983" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2983" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2983" s="3">
+        <v>38</v>
+      </c>
+      <c r="F2983" s="9">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2984" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2984" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2984" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2984" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2984" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2984" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2984" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2985" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2985" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2985" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2985" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2985" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2985" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2985" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2986" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2986" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2986" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2986" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2986" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2986" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2986" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2987" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2987" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2987" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2987" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2987" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2987" s="3">
+        <v>506</v>
+      </c>
+      <c r="F2987" s="9">
+        <v>0.90200000000000002</v>
+      </c>
+    </row>
+    <row r="2988" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2988" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2988" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2988" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2988" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2988" s="3">
+        <v>40</v>
+      </c>
+      <c r="F2988" s="9">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="2989" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2989" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2989" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2989" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2989" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2989" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2989" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2990" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2990" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2990" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2990" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2990" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2990" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2990" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2991" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2991" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2991" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2991" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2991" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2991" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2991" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2992" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2992" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2992" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2992" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2992" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2992" s="3">
+        <v>70</v>
+      </c>
+      <c r="F2992" s="9">
+        <v>0.86399999999999999</v>
+      </c>
+    </row>
+    <row r="2993" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2993" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2993" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2993" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2993" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2993" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2993" s="9">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="2994" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2994" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2994" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2994" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2994" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2994" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2994" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2995" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2995" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2995" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2995" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2995" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2995" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2995" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2996" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2996" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2996" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2996" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2996" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2996" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2996" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2997" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2997" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2997" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2997" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2997" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2997" s="3">
+        <v>157</v>
+      </c>
+      <c r="F2997" s="9">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
+    <row r="2998" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2998" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2998" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2998" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2998" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2998" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2998" s="9">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2999" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2999" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2999" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2999" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2999" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2999" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2999" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="3000" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3000" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3000" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3000" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3000" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3000" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3000" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3001" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3001" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3001" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3001" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3001" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3001" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3001" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3002" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3002" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3002" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3002" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3002" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3002" s="3">
+        <v>76</v>
+      </c>
+      <c r="F3002" s="9">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="3003" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3003" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3003" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3003" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3003" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3003" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3003" s="9">
+        <v>7.2999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="3004" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3004" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3004" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3004" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3004" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3004" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3004" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3005" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3005" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3005" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3005" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3005" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3005" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3005" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3006" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3006" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3006" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3006" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3006" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3006" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3006" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A4B614-C1AD-4CD0-A5D3-EADC99313905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAE4652-9DB1-459F-9B62-1525077DB2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6284" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6336" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3689,6 +3689,29 @@
         <v>82</v>
       </c>
     </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>2026</v>
+      </c>
+      <c r="B129" t="s">
+        <v>47</v>
+      </c>
+      <c r="C129">
+        <v>716</v>
+      </c>
+      <c r="D129">
+        <v>534</v>
+      </c>
+      <c r="E129">
+        <v>120</v>
+      </c>
+      <c r="F129">
+        <v>171</v>
+      </c>
+      <c r="G129" s="17">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3697,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6565,6 +6588,29 @@
       </c>
       <c r="G128">
         <v>4.93</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>2026</v>
+      </c>
+      <c r="B129" t="s">
+        <v>47</v>
+      </c>
+      <c r="C129">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D129">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E129">
+        <v>4.83</v>
+      </c>
+      <c r="F129">
+        <v>4.92</v>
+      </c>
+      <c r="G129">
+        <v>4.8899999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -6575,7 +6621,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L3006"/>
+  <dimension ref="A1:L3031"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -66746,6 +66792,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3007" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3007" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3007" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3007" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3007" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3007" s="3">
+        <v>661</v>
+      </c>
+      <c r="F3007" s="9">
+        <v>0.92300000000000004</v>
+      </c>
+    </row>
+    <row r="3008" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3008" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3008" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3008" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3008" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3008" s="3">
+        <v>45</v>
+      </c>
+      <c r="F3008" s="9">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="3009" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3009" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3009" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3009" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3009" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3009" s="3">
+        <v>7</v>
+      </c>
+      <c r="F3009" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3010" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3010" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3010" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3010" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3010" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3010" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3010" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3011" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3011" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3011" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3011" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3011" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3011" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="3012" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3012" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3012" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3012" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3012" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3012" s="3">
+        <v>500</v>
+      </c>
+      <c r="F3012" s="9">
+        <v>0.93600000000000005</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3013" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3013" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3013" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3013" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3013" s="3">
+        <v>23</v>
+      </c>
+      <c r="F3013" s="9">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3014" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3014" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3014" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3014" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3014" s="3">
+        <v>7</v>
+      </c>
+      <c r="F3014" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3015" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3015" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3015" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3015" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3015" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3015" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3016" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3016" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3016" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3016" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3016" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3016" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3017" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3017" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3017" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3017" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3017" s="3">
+        <v>104</v>
+      </c>
+      <c r="F3017" s="9">
+        <v>0.86699999999999999</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3018" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3018" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3018" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3018" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3018" s="3">
+        <v>13</v>
+      </c>
+      <c r="F3018" s="9">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3019" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3019" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3019" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3019" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3019" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3019" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3020" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3020" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3020" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3020" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3020" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3020" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3021" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3021" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3021" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3021" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3021" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3021" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3022" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3022" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3022" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3022" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3022" s="3">
+        <v>160</v>
+      </c>
+      <c r="F3022" s="9">
+        <v>0.93600000000000005</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3023" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3023" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3023" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3023" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3023" s="3">
+        <v>8</v>
+      </c>
+      <c r="F3023" s="9">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3024" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3024" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3024" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3024" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3024" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3024" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3025" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3025" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3025" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3025" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3025" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3025" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3026" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3026" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3026" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3026" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3026" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3026" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3027" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3027" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3027" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3027" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3027" s="3">
+        <v>70</v>
+      </c>
+      <c r="F3027" s="9">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3028" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3028" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3028" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3028" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3028" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3028" s="9">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3029" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3029" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3029" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3029" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3029" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3029" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3030" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3030" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3030" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3030" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3030" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3030" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3031" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3031" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3031" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3031" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3031" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3031" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAE4652-9DB1-459F-9B62-1525077DB2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F24261-0D59-4851-B50D-5B7951983E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6336" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6388" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3712,6 +3712,29 @@
         <v>76</v>
       </c>
     </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>2026</v>
+      </c>
+      <c r="B130" t="s">
+        <v>48</v>
+      </c>
+      <c r="C130">
+        <v>668</v>
+      </c>
+      <c r="D130">
+        <v>600</v>
+      </c>
+      <c r="E130">
+        <v>107</v>
+      </c>
+      <c r="F130">
+        <v>172</v>
+      </c>
+      <c r="G130" s="17">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3720,7 +3743,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6610,6 +6633,29 @@
         <v>4.92</v>
       </c>
       <c r="G129">
+        <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>2026</v>
+      </c>
+      <c r="B130" t="s">
+        <v>48</v>
+      </c>
+      <c r="C130">
+        <v>4.91</v>
+      </c>
+      <c r="D130">
+        <v>4.88</v>
+      </c>
+      <c r="E130">
+        <v>4.74</v>
+      </c>
+      <c r="F130">
+        <v>4.8</v>
+      </c>
+      <c r="G130">
         <v>4.8899999999999997</v>
       </c>
     </row>
@@ -6621,7 +6667,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L3031"/>
+  <dimension ref="A1:L3056"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -67292,6 +67338,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3032" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3032" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3032" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3032" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3032" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3032" s="3">
+        <v>621</v>
+      </c>
+      <c r="F3032" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3033" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3033" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3033" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3033" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3033" s="3">
+        <v>38</v>
+      </c>
+      <c r="F3033" s="9">
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3034" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3034" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3034" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3034" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3034" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3034" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3035" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3035" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3035" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3035" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3035" s="3">
+        <v>4</v>
+      </c>
+      <c r="F3035" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3036" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3036" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3036" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3036" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3036" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3036" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3037" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3037" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3037" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3037" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3037" s="3">
+        <v>549</v>
+      </c>
+      <c r="F3037" s="9">
+        <v>0.91500000000000004</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3038" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3038" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3038" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3038" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3038" s="3">
+        <v>36</v>
+      </c>
+      <c r="F3038" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3039" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3039" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3039" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3039" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3039" s="3">
+        <v>12</v>
+      </c>
+      <c r="F3039" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3040" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3040" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3040" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3040" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3040" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3040" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3041" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3041" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3041" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3041" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3041" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3041" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3042" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3042" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3042" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3042" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3042" s="3">
+        <v>90</v>
+      </c>
+      <c r="F3042" s="9">
+        <v>0.84099999999999997</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3043" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3043" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3043" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3043" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3043" s="3">
+        <v>9</v>
+      </c>
+      <c r="F3043" s="9">
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3044" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3044" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3044" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3044" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3044" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3044" s="9">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3045" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3045" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3045" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3045" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3045" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3045" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3046" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3046" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3046" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3046" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3046" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3046" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3047" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3047" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3047" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3047" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3047" s="3">
+        <v>147</v>
+      </c>
+      <c r="F3047" s="9">
+        <v>0.85499999999999998</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3048" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3048" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3048" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3048" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3048" s="3">
+        <v>18</v>
+      </c>
+      <c r="F3048" s="9">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3049" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3049" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3049" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3049" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3049" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3049" s="9">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3050" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3050" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3050" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3050" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3050" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3050" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3051" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3051" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3051" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3051" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3051" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3051" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3052" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3052" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3052" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3052" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3052" s="3">
+        <v>89</v>
+      </c>
+      <c r="F3052" s="9">
+        <v>0.95699999999999996</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3053" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3053" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3053" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3053" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3053" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3053" s="9">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3054" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3054" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3054" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3054" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3054" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3054" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3055" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3055" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3055" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3055" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3055" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3055" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3056" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3056" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3056" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3056" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3056" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3056" s="9">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F24261-0D59-4851-B50D-5B7951983E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A5EDD8-6E53-41FA-9A16-460FABA6D2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6388" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6440" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3735,6 +3735,29 @@
         <v>93</v>
       </c>
     </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>2026</v>
+      </c>
+      <c r="B131" t="s">
+        <v>49</v>
+      </c>
+      <c r="C131">
+        <v>532</v>
+      </c>
+      <c r="D131">
+        <v>521</v>
+      </c>
+      <c r="E131">
+        <v>100</v>
+      </c>
+      <c r="F131">
+        <v>113</v>
+      </c>
+      <c r="G131" s="17">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3743,7 +3766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6657,6 +6680,29 @@
       </c>
       <c r="G130">
         <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>2026</v>
+      </c>
+      <c r="B131" t="s">
+        <v>49</v>
+      </c>
+      <c r="C131">
+        <v>4.87</v>
+      </c>
+      <c r="D131">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E131">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F131">
+        <v>4.91</v>
+      </c>
+      <c r="G131">
+        <v>4.9400000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -6667,7 +6713,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L3056"/>
+  <dimension ref="A1:L3081"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -67838,6 +67884,506 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
+    <row r="3057" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3057" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3057" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3057" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3057" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3057" s="3">
+        <v>479</v>
+      </c>
+      <c r="F3057" s="9">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3058" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3058" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3058" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3058" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3058" s="3">
+        <v>39</v>
+      </c>
+      <c r="F3058" s="9">
+        <v>7.2999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3059" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3059" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3059" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3059" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3059" s="3">
+        <v>14</v>
+      </c>
+      <c r="F3059" s="9">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3060" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3060" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3060" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3060" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3060" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3060" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3061" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3061" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3061" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3061" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3061" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3061" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3062" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3062" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3062" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3062" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3062" s="3">
+        <v>483</v>
+      </c>
+      <c r="F3062" s="9">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3063" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3063" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3063" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3063" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3063" s="3">
+        <v>31</v>
+      </c>
+      <c r="F3063" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3064" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3064" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3064" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3064" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3064" s="3">
+        <v>4</v>
+      </c>
+      <c r="F3064" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3065" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3065" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3065" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3065" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3065" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3065" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3066" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3066" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3066" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3066" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3066" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3066" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3067" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3067" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3067" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3067" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3067" s="3">
+        <v>82</v>
+      </c>
+      <c r="F3067" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3068" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3068" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3068" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3068" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3068" s="3">
+        <v>13</v>
+      </c>
+      <c r="F3068" s="9">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="3069" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3069" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3069" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3069" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3069" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3069" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3069" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3070" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3070" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3070" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3070" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3070" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3070" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3071" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3071" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3071" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3071" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3071" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3071" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3072" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3072" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3072" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3072" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3072" s="3">
+        <v>105</v>
+      </c>
+      <c r="F3072" s="9">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3073" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3073" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3073" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3073" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3073" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3073" s="9">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3074" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3074" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3074" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3074" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3074" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3074" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3075" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3075" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3075" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3075" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3075" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3075" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3075" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3076" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3076" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3076" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3076" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3076" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3076" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3076" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3077" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3077" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3077" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3077" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3077" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3077" s="3">
+        <v>45</v>
+      </c>
+      <c r="F3077" s="9">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="3078" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3078" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3078" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3078" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3078" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3078" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3078" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="3079" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3079" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3079" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3079" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3079" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3079" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3079" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3080" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3080" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3080" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3080" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3080" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3080" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3080" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3081" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3081" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3081" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3081" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3081" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3081" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3081" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A5EDD8-6E53-41FA-9A16-460FABA6D2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF778F4-1E17-40A0-AAE1-D8C6866FED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6440" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6492" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3758,6 +3758,29 @@
         <v>48</v>
       </c>
     </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>2026</v>
+      </c>
+      <c r="B132" t="s">
+        <v>50</v>
+      </c>
+      <c r="C132">
+        <v>662</v>
+      </c>
+      <c r="D132">
+        <v>613</v>
+      </c>
+      <c r="E132">
+        <v>123</v>
+      </c>
+      <c r="F132">
+        <v>190</v>
+      </c>
+      <c r="G132" s="17">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3766,7 +3789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6703,6 +6726,29 @@
       </c>
       <c r="G131">
         <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>2026</v>
+      </c>
+      <c r="B132" t="s">
+        <v>50</v>
+      </c>
+      <c r="C132">
+        <v>4.93</v>
+      </c>
+      <c r="D132">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E132">
+        <v>4.83</v>
+      </c>
+      <c r="F132">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G132">
+        <v>4.8600000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -6713,7 +6759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L3081"/>
+  <dimension ref="A1:L3106"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -68384,6 +68430,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3082" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3082" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3082" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3082" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3082" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3082" s="3">
+        <v>622</v>
+      </c>
+      <c r="F3082" s="9">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="3083" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3083" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3083" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3083" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3083" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3083" s="3">
+        <v>34</v>
+      </c>
+      <c r="F3083" s="9">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3084" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3084" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3084" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3084" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3084" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3084" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3084" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="3085" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3085" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3085" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3085" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3085" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3085" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3085" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3086" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3086" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3086" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3086" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3086" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3086" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3086" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3087" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3087" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3087" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3087" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3087" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3087" s="3">
+        <v>567</v>
+      </c>
+      <c r="F3087" s="9">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="3088" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3088" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3088" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3088" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3088" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3088" s="3">
+        <v>37</v>
+      </c>
+      <c r="F3088" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="3089" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3089" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3089" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3089" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3089" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3089" s="3">
+        <v>7</v>
+      </c>
+      <c r="F3089" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3090" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3090" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3090" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3090" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3090" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3090" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3090" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3091" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3091" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3091" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3091" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3091" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3091" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3091" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3092" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3092" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3092" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3092" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3092" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3092" s="3">
+        <v>105</v>
+      </c>
+      <c r="F3092" s="9">
+        <v>0.85399999999999998</v>
+      </c>
+    </row>
+    <row r="3093" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3093" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3093" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3093" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3093" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3093" s="3">
+        <v>15</v>
+      </c>
+      <c r="F3093" s="9">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="3094" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3094" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3094" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3094" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3094" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3094" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3094" s="9">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="3095" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3095" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3095" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3095" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3095" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3095" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3095" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3096" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3096" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3096" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3096" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3096" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3096" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3096" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3097" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3097" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3097" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3097" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3097" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3097" s="3">
+        <v>173</v>
+      </c>
+      <c r="F3097" s="9">
+        <v>0.91100000000000003</v>
+      </c>
+    </row>
+    <row r="3098" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3098" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3098" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3098" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3098" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3098" s="3">
+        <v>15</v>
+      </c>
+      <c r="F3098" s="9">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3099" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3099" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3099" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3099" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3099" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3099" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3099" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3100" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3100" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3100" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3100" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3101" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3101" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3101" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3102" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3102" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3102" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3102" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3102" s="3">
+        <v>65</v>
+      </c>
+      <c r="F3102" s="9">
+        <v>0.878</v>
+      </c>
+    </row>
+    <row r="3103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3103" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3103" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3103" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3103" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3103" s="3">
+        <v>8</v>
+      </c>
+      <c r="F3103" s="9">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="3104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3104" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3104" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3104" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3104" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3104" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3104" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="3105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3105" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3105" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3105" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3105" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3105" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3105" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3106" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3106" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3106" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3106" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF778F4-1E17-40A0-AAE1-D8C6866FED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CC2F7D-BBA6-4DA4-8EAE-9C098BFB2F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6492" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6544" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3781,6 +3781,29 @@
         <v>74</v>
       </c>
     </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>2026</v>
+      </c>
+      <c r="B133" t="s">
+        <v>51</v>
+      </c>
+      <c r="C133">
+        <v>727</v>
+      </c>
+      <c r="D133">
+        <v>645</v>
+      </c>
+      <c r="E133">
+        <v>111</v>
+      </c>
+      <c r="F133">
+        <v>186</v>
+      </c>
+      <c r="G133" s="17">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3789,7 +3812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6749,6 +6772,29 @@
       </c>
       <c r="G132">
         <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>2026</v>
+      </c>
+      <c r="B133" t="s">
+        <v>51</v>
+      </c>
+      <c r="C133">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D133">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E133">
+        <v>4.78</v>
+      </c>
+      <c r="F133">
+        <v>4.82</v>
+      </c>
+      <c r="G133">
+        <v>4.88</v>
       </c>
     </row>
   </sheetData>
@@ -6759,7 +6805,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L3106"/>
+  <dimension ref="A1:L3131"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -68930,6 +68976,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3107" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3107" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3107" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3107" s="3">
+        <v>675</v>
+      </c>
+      <c r="F3107" s="9">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="3108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3108" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3108" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3108" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3108" s="3">
+        <v>39</v>
+      </c>
+      <c r="F3108" s="9">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3109" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3109" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3109" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3109" s="3">
+        <v>10</v>
+      </c>
+      <c r="F3109" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="3110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3110" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3110" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3110" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3110" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3110" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="3111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3111" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3111" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3111" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3111" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3111" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3112" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3112" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3112" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3112" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3112" s="3">
+        <v>590</v>
+      </c>
+      <c r="F3112" s="9">
+        <v>0.91500000000000004</v>
+      </c>
+    </row>
+    <row r="3113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3113" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3113" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3113" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3113" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3113" s="3">
+        <v>40</v>
+      </c>
+      <c r="F3113" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="3114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3114" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3114" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3114" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3114" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3114" s="3">
+        <v>14</v>
+      </c>
+      <c r="F3114" s="9">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3115" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3115" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3115" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3115" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3115" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3115" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3116" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3116" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3116" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3116" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3116" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="3117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3117" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3117" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3117" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3117" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3117" s="3">
+        <v>94</v>
+      </c>
+      <c r="F3117" s="9">
+        <v>0.84699999999999998</v>
+      </c>
+    </row>
+    <row r="3118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3118" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3118" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3118" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3118" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3118" s="3">
+        <v>14</v>
+      </c>
+      <c r="F3118" s="9">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="3119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3119" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3119" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3119" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3119" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3119" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3119" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="3120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3120" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3120" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3120" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3120" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3120" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3120" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3121" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3121" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3121" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3121" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3121" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3122" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3122" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3122" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3122" s="3">
+        <v>162</v>
+      </c>
+      <c r="F3122" s="9">
+        <v>0.871</v>
+      </c>
+    </row>
+    <row r="3123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3123" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3123" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3123" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3123" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3123" s="3">
+        <v>16</v>
+      </c>
+      <c r="F3123" s="9">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="3124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3124" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3124" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3124" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3124" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3124" s="3">
+        <v>7</v>
+      </c>
+      <c r="F3124" s="9">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3125" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3125" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3125" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3125" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3125" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3125" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3126" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3126" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3126" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3126" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3127" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3127" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3127" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3127" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3127" s="3">
+        <v>62</v>
+      </c>
+      <c r="F3127" s="9">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="3128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3128" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3128" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3128" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3128" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3128" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3128" s="9">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="3129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3129" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3129" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3129" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3129" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3129" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3129" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3130" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3130" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3130" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3130" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3130" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3130" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3131" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3131" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3131" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3131" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3131" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3131" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CC2F7D-BBA6-4DA4-8EAE-9C098BFB2F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1190B0A-E135-4078-9CD0-E6AC293E149A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6544" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3804,6 +3804,29 @@
         <v>67</v>
       </c>
     </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>2026</v>
+      </c>
+      <c r="B134" t="s">
+        <v>52</v>
+      </c>
+      <c r="C134">
+        <v>726</v>
+      </c>
+      <c r="D134">
+        <v>628</v>
+      </c>
+      <c r="E134">
+        <v>123</v>
+      </c>
+      <c r="F134">
+        <v>204</v>
+      </c>
+      <c r="G134" s="17">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3812,7 +3835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6795,6 +6818,29 @@
       </c>
       <c r="G133">
         <v>4.88</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>2026</v>
+      </c>
+      <c r="B134" t="s">
+        <v>52</v>
+      </c>
+      <c r="C134">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D134">
+        <v>4.87</v>
+      </c>
+      <c r="E134">
+        <v>4.76</v>
+      </c>
+      <c r="F134">
+        <v>4.84</v>
+      </c>
+      <c r="G134">
+        <v>4.9400000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -6805,7 +6851,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L3131"/>
+  <dimension ref="A1:L3156"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -69476,6 +69522,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3132" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3132" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3132" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3132" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3132" s="3">
+        <v>670</v>
+      </c>
+      <c r="F3132" s="9">
+        <v>0.92300000000000004</v>
+      </c>
+    </row>
+    <row r="3133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3133" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3133" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3133" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3133" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3133" s="3">
+        <v>38</v>
+      </c>
+      <c r="F3133" s="9">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="3134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3134" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3134" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3134" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3134" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3134" s="3">
+        <v>16</v>
+      </c>
+      <c r="F3134" s="9">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3135" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3135" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3135" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3135" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3135" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3135" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3136" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3136" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3136" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3136" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3136" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3137" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3137" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3137" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3137" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3137" s="3">
+        <v>570</v>
+      </c>
+      <c r="F3137" s="9">
+        <v>0.90800000000000003</v>
+      </c>
+    </row>
+    <row r="3138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3138" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3138" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3138" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3138" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3138" s="3">
+        <v>45</v>
+      </c>
+      <c r="F3138" s="9">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="3139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3139" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3139" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3139" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3139" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3139" s="3">
+        <v>8</v>
+      </c>
+      <c r="F3139" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3140" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3140" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3140" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3140" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3140" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3140" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="3141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3141" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3141" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3141" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3141" s="3">
+        <v>4</v>
+      </c>
+      <c r="F3141" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3142" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3142" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3142" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3142" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3142" s="3">
+        <v>102</v>
+      </c>
+      <c r="F3142" s="9">
+        <v>0.82899999999999996</v>
+      </c>
+    </row>
+    <row r="3143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3143" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3143" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3143" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3143" s="3">
+        <v>14</v>
+      </c>
+      <c r="F3143" s="9">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="3144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3144" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3144" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3144" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3144" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3144" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3144" s="9">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="3145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3145" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3145" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3145" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3145" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3145" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3145" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3146" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3146" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3146" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3146" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3146" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="3147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3147" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3147" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3147" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3147" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3147" s="3">
+        <v>183</v>
+      </c>
+      <c r="F3147" s="9">
+        <v>0.89700000000000002</v>
+      </c>
+    </row>
+    <row r="3148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3148" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3148" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3148" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3148" s="3">
+        <v>16</v>
+      </c>
+      <c r="F3148" s="9">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="3149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3149" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3149" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3149" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3149" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3149" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3149" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3150" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3150" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3150" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3150" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3150" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3150" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3151" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3151" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3151" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3151" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3151" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3151" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3152" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3152" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3152" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3152" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3152" s="3">
+        <v>82</v>
+      </c>
+      <c r="F3152" s="9">
+        <v>0.95299999999999996</v>
+      </c>
+    </row>
+    <row r="3153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3153" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3153" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3153" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3153" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3153" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3153" s="9">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="3154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3154" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3154" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3154" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3154" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3154" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3154" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="3155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3155" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3155" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3155" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3155" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3155" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3155" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3156" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3156" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3156" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3156" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3156" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3156" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1190B0A-E135-4078-9CD0-E6AC293E149A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2AE647-7016-4206-ABCE-289C1D8EE1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6648" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3827,6 +3827,29 @@
         <v>86</v>
       </c>
     </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>2026</v>
+      </c>
+      <c r="B135" t="s">
+        <v>53</v>
+      </c>
+      <c r="C135">
+        <v>666</v>
+      </c>
+      <c r="D135">
+        <v>564</v>
+      </c>
+      <c r="E135">
+        <v>101</v>
+      </c>
+      <c r="F135">
+        <v>177</v>
+      </c>
+      <c r="G135" s="17">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3835,7 +3858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K134"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6841,6 +6864,29 @@
       </c>
       <c r="G134">
         <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>2026</v>
+      </c>
+      <c r="B135" t="s">
+        <v>53</v>
+      </c>
+      <c r="C135">
+        <v>4.91</v>
+      </c>
+      <c r="D135">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E135">
+        <v>4.87</v>
+      </c>
+      <c r="F135">
+        <v>4.82</v>
+      </c>
+      <c r="G135">
+        <v>4.92</v>
       </c>
     </row>
   </sheetData>
@@ -6851,7 +6897,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L3156"/>
+  <dimension ref="A1:L3181"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -70022,6 +70068,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3157" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3157" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3157" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3157" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3157" s="3">
+        <v>617</v>
+      </c>
+      <c r="F3157" s="9">
+        <v>0.92600000000000005</v>
+      </c>
+    </row>
+    <row r="3158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3158" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3158" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3158" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3158" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3158" s="3">
+        <v>38</v>
+      </c>
+      <c r="F3158" s="9">
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="3159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3159" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3159" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3159" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3159" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3159" s="3">
+        <v>8</v>
+      </c>
+      <c r="F3159" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="3160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3160" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3160" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3160" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3160" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3160" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3160" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3161" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3161" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3161" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3161" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3161" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3161" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3162" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3162" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3162" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3162" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3162" s="3">
+        <v>520</v>
+      </c>
+      <c r="F3162" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="3163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3163" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3163" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3163" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3163" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3163" s="3">
+        <v>30</v>
+      </c>
+      <c r="F3163" s="9">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3164" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3164" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3164" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3164" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3164" s="3">
+        <v>11</v>
+      </c>
+      <c r="F3164" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="3165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3165" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3165" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3165" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3165" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3165" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3165" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3166" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3166" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3166" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3166" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3166" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3166" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3167" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3167" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3167" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3167" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3167" s="3">
+        <v>93</v>
+      </c>
+      <c r="F3167" s="9">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="3168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3168" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3168" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3168" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3168" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3168" s="9">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3169" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3169" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3169" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3169" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3169" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3169" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3170" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3170" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3170" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3170" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3170" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3170" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3171" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3171" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3171" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3171" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3171" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3171" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3172" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3172" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3172" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3172" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3172" s="3">
+        <v>158</v>
+      </c>
+      <c r="F3172" s="9">
+        <v>0.89300000000000002</v>
+      </c>
+    </row>
+    <row r="3173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3173" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3173" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3173" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3173" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3173" s="3">
+        <v>10</v>
+      </c>
+      <c r="F3173" s="9">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3174" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3174" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3174" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3174" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3174" s="3">
+        <v>7</v>
+      </c>
+      <c r="F3174" s="9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="3175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3175" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3175" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3175" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3175" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3175" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3175" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3176" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3176" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3176" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3176" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3176" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3176" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3177" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3177" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3177" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3177" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3177" s="3">
+        <v>86</v>
+      </c>
+      <c r="F3177" s="9">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="3178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3178" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3178" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3178" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3178" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3178" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3178" s="9">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3179" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3179" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3179" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3179" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3179" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3179" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3180" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3180" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3180" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3180" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3180" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3180" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3181" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3181" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3181" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3181" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3181" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3181" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>
